--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_29-09-2026.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_29-09-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="295">
   <si>
     <t>SKU</t>
   </si>
@@ -460,10 +460,7 @@
     <t>£35.00</t>
   </si>
   <si>
-    <t>Home Insulation Loft Insulation Loft Insulation Slabs Knauf Insulation DriTherm Cavity Slab 37 75mm - 4.37m2 Pack Knauf Insulation DriTherm Cavity Slab 37 75mm - 4.37m2 Pack Code: 1994-316654 Brand: Knauf Pack Quantity: Price per : Free Knauf delivery on orders over £500 ex VAT Keep external masonry walls better insulated with Knauf DriTherm Cavity Slab 37, a flexible full-fill solution combining reliable thermal performance with easy installation. Its water-repellent glass mineral wool construction achieves a thermal conductivity of 0.037W/mK, while... Read More View full product details Ask a question about this product POA Enquire Online Or call our friendly team on 01752 692 206 Est. Delivery: 2-3 Working Days Shipping costs displayed in basket. We can let you know when this product is back in stock. This product is proving to be very popular and has unfortunately sold out. Enter your email below and we'll notify you as soon as this product is back in stock: Email Sign up for our email newsletter For delivery Wednesday, Sep 30th - order in: 0 days 3 hrs 9 mins 11 secs For delivery Wednesday, Sep 30th - order in: 0 days 3 hrs 9 mins 11 secs View Transport Policy Next day delivery is subject to stock availability. If products on a 24 hours service are ordered alongside products NOT on a 24 hours service, this may delay your whole order. All delivery charges are included in the final shopping basket and are dependent on the products Scottish Highlands &amp; the Islands where additional shipping charges will apply. Please note that not all products will incur an additional delivery charge to the Scottish Highlands &amp; the Islands – this is based on the costs from the manufacturer, distributor or courier providing shipping on our behalf. If your delivery address is in the Scottish Highlands and Islands, a member of our helpline team will contact you prior to processing your order should an additional delivery charge apply. While we make every effort to ensure orders are delivered by the date required, we cannot guarantee availability from the manufacturer or the manufacturer's delivery schedules. Any variation to web delivery date given will be advised to you by email or telephone. If we are unable to make delivery because access is not possible, we reserve the right to make a failed delivery charge. See Full Transport Policy View full product details Ask a question about this product Create a wishlist Add to a wishlist ADD Oops! Please select from the options Create a wishlist Frequently Bought Together "Insulation at a good price" William Davies Description Specification Downloads Q&amp;A Description Keep external masonry walls better insulated with Knauf DriTherm Cavity Slab 37, a flexible full-fill solution combining reliable thermal performance with easy installation. Its water-repellent glass mineral wool construction achieves a thermal conductivity of 0.037W/mK, while plant-based ECOSE Technology provides a more sustainable binder. For added fire performance, the material is non-combustible and rated Euroclass A1. Rather than leaving gaps around small surface irregularities, the adaptable slabs mould closely to the substrate and knit together for consistent insulation across the cavity. Their lightweight design makes cutting and positioning simple, with a friction fit between wall ties removing the need for retaining discs. Features &amp; Benefits: Knauf Insulation DriTherm Cavity Slab 37 75mm - 4.37m2 Pack 4.37m pack coverage with eight slabs in a pack Water repellent and non-combustible Thermal conductivity of 0.037 W/mK Crafted from glass mineral wool 2.0 mK/W R-Value Water vapour resistivity: 5.00 MNs/g.m Close-fitting structure reduces unwanted air gaps These slabs are compatible with buildings in any exposure zone, including harsh areas as they are BBA-certified. They can used in structures up to 12m in height and multi-storey buildings up to 25m tall if they meet the BBA certification criteria. Supplied in recyclable polythene packs (4-LDPE), short-term protection is provided. Standards &amp; Certification Awarded the DECLARE 'Red List Free' label: Free from any harmful chemicals listed on the Living Building Challenge (LBC) Red List Reaction to fire: A1 Euroclass classification to BS EN 13501-1 Certified by TV Nord: Manufactured in accordance with BS EN 13162, ISO 50001 Energy Management Systems, ISO 14001 Environmental Management Systems and ISO 9001 Quality Management systems EPD Standard: EN 15804 BBA Certification No: 95/3212 Green Guide Rating: A+ BBA certified: for all exposure zones, including very severe conditions CCPI Verification Mark: 000600006/0426 Please note: For long-term storage on-site, it is recommended that you keep this Knauf DriTherm insulation indoors or covered and off the ground to maintain its effectiveness as exposure to the elements can impact its performance. Specification Dimensions Length 1200mm Depth 75mm Width 455mm Details Thickness 75mm Thermal Conductivity 0.037 W/mK Application Cavity Wall Features Fire Protection Fire Performance Class 1 Material Glass Wool Coverage 4.37m2 Range Dritherm 37 Slab Size 455mm x 1200mm Downloads Safety Data Sheet (PDF) Other Certification (PDF) BBA Certificate (PDF) Installation Guide (PDF) Product Brochure (PDF) EPD (PDF) Questions &amp; Answers There are currently no questions for this product. Have a question about this product? Question Name Email Telephone Submit Products We Recommend Loftleg Insulation Loft Flooring Leg 175mm - Box of 12 £13.34 Ex. VAT £16.01 Incl. VAT £13.34 Ex. VAT Loftleg Loft Ledge Truss Shelving Kit 530mm x 530mm £7.71 Ex. VAT £9.25 Incl. VAT £7.71 Ex. VAT Loftleg Loft Lid Downlight Cover £6.45 Ex. VAT £7.74 Incl. VAT £6.45 Ex. VAT Stanley FATMAX Fixed Blade Folding Knife £15.00 Ex. VAT £18.00 Incl. VAT £15.00 Ex. VAT Knauf Guides &amp; Articles Part L Building Regulations Explained (Volume One – Dwellings) Insulation is an efficient and must-have solution to conserve energy; that’s why we have an Approved Document dedicated to it. With that said, there’s a lot of information to  ... More Insulating a floor Floor insulation is a super way to keep your property warm, while also being cost-effective in terms of your energy bills and the insulation you need to buy for your project. When we thin ... More Glass wool or mineral wool – which is best for insulation? When you’re insulating a building, it is important to ensure you have the best materials for the job. Fibreglass and mineral wool are two of the more popular types of insulation for ... More All Product Enquiry Form Knauf Insulation DriTherm Cavity Slab 37 75mm - 4.37m2 Pack Name * Telephone * Email * Delivery Postcode * Access Restrictions * Quantity Required Date Required Comments Signup for deal emails Optional. You can unsubscribe at any time. Yes, I would like to get up-to-date information including exclusive deals and latest product news. * Required Field Do Not Fill This Out Log in to create wishlist Please enter your details below highlighted in red. Forgotten your password? New customer? Register Create a wishlist Please only use alphanumeric characters, spaces and hyphens. The name also has to be 100 characters or fewer.</t>
-  </si>
-  <si>
-    <t>Home Insulation Loft Insulation Loft Insulation Slabs Knauf Insulation DriTherm Cavity Slab 37 100mm - 6.55m2 Pack Knauf Insulation DriTherm Cavity Slab 37 100mm - 6.55m2 Pack Code: 001994-715831 Brand: Knauf Pack Quantity: Price per : Free Knauf delivery on orders over £500 ex VAT Knauf DriTherm Cavity Slab 37 offers reliable thermal insulation for external full-fill masonry cavity walls. Manufactured from water-repellent glass mineral wool using plant-based ECOSE Technology, it delivers a thermal conductivity of 0.037W/mK and an R-value of 2.70mK/W. No... Read More View full product details Ask a question about this product POA Enquire Online Or call our friendly team on 01752 692 206 Est. Delivery: 2-3 Working Days Shipping costs displayed in basket. We can let you know when this product is back in stock. This product is proving to be very popular and has unfortunately sold out. Enter your email below and we'll notify you as soon as this product is back in stock: Email Sign up for our email newsletter For delivery Wednesday, Sep 30th - order in: 0 days 3 hrs 7 mins 52 secs For delivery Wednesday, Sep 30th - order in: 0 days 3 hrs 7 mins 52 secs View Transport Policy Next day delivery is subject to stock availability. If products on a 24 hours service are ordered alongside products NOT on a 24 hours service, this may delay your whole order. All delivery charges are included in the final shopping basket and are dependent on the products Scottish Highlands &amp; the Islands where additional shipping charges will apply. Please note that not all products will incur an additional delivery charge to the Scottish Highlands &amp; the Islands – this is based on the costs from the manufacturer, distributor or courier providing shipping on our behalf. If your delivery address is in the Scottish Highlands and Islands, a member of our helpline team will contact you prior to processing your order should an additional delivery charge apply. While we make every effort to ensure orders are delivered by the date required, we cannot guarantee availability from the manufacturer or the manufacturer's delivery schedules. Any variation to web delivery date given will be advised to you by email or telephone. If we are unable to make delivery because access is not possible, we reserve the right to make a failed delivery charge. See Full Transport Policy View full product details Ask a question about this product Create a wishlist Add to a wishlist ADD Oops! Please select from the options Create a wishlist Frequently Bought Together "Excellent service" Mr Steve Houldridge Description Specification Downloads Q&amp;A Description Knauf DriTherm Cavity Slab 37 offers reliable thermal insulation for external full-fill masonry cavity walls. Manufactured from water-repellent glass mineral wool using plant-based ECOSE Technology, it delivers a thermal conductivity of 0.037W/mK and an R-value of 2.70mK/W. Non-combustible with a Euroclass A1 reaction to fire classification, it provides an effective combination of thermal and fire performance. Lightweight and easy to cut and install, the flexible slabs adapt to minor substrate imperfections and knit together to minimise air gaps. They fit securely between wall ties without retaining discs and are BBA certified for all exposure zones, including very severe conditions. Features &amp; Benefits: Knauf Insulation DriTherm Cavity Slab 37 100mm - 6.55m2 Pack Made with a water-repellent additive to resist moisture ingress Friction fits between wall ties No retaining discs or jointing tape needed Full-fill solution that doesn't require cavity barriers Each pack contains 12 slabs measuring 1200 x 455 x 100mm, covering 6.55m2 Standards &amp; Certification Certified by TV Nord: Manufactured in accordance with BS EN 13162, ISO 50001 Energy Management Systems, ISO 14001 Environmental Management Systems and ISO 9001 Quality Management systems Awarded the DECLARE 'Red List Free' label: Free from any harmful chemicals listed on the Living Building Challenge (LBC) Red List BBA Certification No: 95/3212 for all exposure zones, including very severe conditions Reaction to fire: A1 Euroclass classification to BS EN 13501-1 Green Guide Rating: A+ EPD Standard: EN 15804 CCPI Verification Mark: 000600006/0426 Please note: For longer-term storage on-site, it is advisable to keep this Knauf DriTherm insulation indoors or covered and off the ground to maintain its effectiveness, as exposure to the elements can affect its performance. Specification Dimensions Length 1200mm Depth 100mm Width 455mm Details Thickness 100mm Thermal Conductivity 0.037 W/mK Application Cavity Wall Features Fire Protection Fire Performance Class 1 Material Glass Wool Coverage 6.55m2 Range Dritherm 37 Slab Size 455mm x 1200mm Downloads Safety Data Sheet (PDF) Other Certification (PDF) BBA Certificate (PDF) Installation Guide (PDF) Product Brochure (PDF) EPD (PDF) Questions &amp; Answers There are currently no questions for this product. Have a question about this product? Question Name Email Telephone Submit Products We Recommend Loftleg Insulation Loft Flooring Leg 175mm - Box of 12 £13.34 Ex. VAT £16.01 Incl. VAT £13.34 Ex. VAT Loftleg Loft Ledge Truss Shelving Kit 530mm x 530mm £7.71 Ex. VAT £9.25 Incl. VAT £7.71 Ex. VAT Loftleg Loft Lid Downlight Cover £6.45 Ex. VAT £7.74 Incl. VAT £6.45 Ex. VAT Stanley FATMAX Fixed Blade Folding Knife £15.00 Ex. VAT £18.00 Incl. VAT £15.00 Ex. VAT Knauf Guides &amp; Articles Part L Building Regulations Explained (Volume One – Dwellings) Insulation is an efficient and must-have solution to conserve energy; that’s why we have an Approved Document dedicated to it. With that said, there’s a lot of information to  ... More Insulating a floor Floor insulation is a super way to keep your property warm, while also being cost-effective in terms of your energy bills and the insulation you need to buy for your project. When we thin ... More Cavity wall insulation buyer’s guide Cavity walls have been a go-to for properties since the 1930s. Almost all homes have them and unless the property was built within the last 20 years, it’s likely those same cavity walls a ... More All Product Enquiry Form Knauf Insulation DriTherm Cavity Slab 37 100mm - 6.55m2 Pack Name * Telephone * Email * Delivery Postcode * Access Restrictions * Quantity Required Date Required Comments Signup for deal emails Optional. You can unsubscribe at any time. Yes, I would like to get up-to-date information including exclusive deals and latest product news. * Required Field Do Not Fill This Out Log in to create wishlist Please enter your details below highlighted in red. Forgotten your password? New customer? Register Create a wishlist Please only use alphanumeric characters, spaces and hyphens. The name also has to be 100 characters or fewer.</t>
+    <t>£13.34</t>
   </si>
   <si>
     <t>N/L</t>
@@ -505,51 +502,140 @@
     <t>£150.00</t>
   </si>
   <si>
-    <t>£94.92</t>
-  </si>
-  <si>
-    <t>£11.25</t>
-  </si>
-  <si>
-    <t>£10.75</t>
-  </si>
-  <si>
-    <t>£11.50</t>
-  </si>
-  <si>
-    <t>Close dialog Do you want... £25 OFF? Plus 40 SUPER rewards points Subscribe to INSULATION SUPERSTORE for your unique discount Get £25 off £500 Orders over £500 ex VAT &amp; shipping, excluding Celotex. No, thanks</t>
-  </si>
-  <si>
-    <t>Price Not Found</t>
-  </si>
-  <si>
-    <t>£25 off! Close dialog Do you want... £25 OFF? Plus 40 SUPER rewards points Subscribe to INSULATION SUPERSTORE for your unique discount Get £25 off £500 Orders over £500 ex VAT &amp; shipping, excluding Celotex. No, thanks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Message: 
+    <t xml:space="preserve">Error: Message: invalid session id: session deleted as the browser has closed the connection
+from disconnected: not connected to DevTools
+  (Session info: chrome=154.0.8037.58); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#invalidsessionidexception
 Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6d263be05+5a55]
-	chromedriver!(No symbol) [0x7ff6d2563230]
-	chromedriver!(No symbol) [0x7ff6d2386e4d]
-	chromedriver!(No symbol) [0x7ff6d23e266d]
-	chromedriver!(No symbol) [0x7ff6d23e292c]
-	chromedriver!(No symbol) [0x7ff6d24359e7]
-	chromedriver!(No symbol) [0x7ff6d243267a]
-	chromedriver!(No symbol) [0x7ff6d23d4412]
-	chromedriver!(No symbol) [0x7ff6d23d5223]
-	chromedriver!GetHandleVerifier [0x7ff6d2a4b1d1+414e21]
-	chromedriver!GetHandleVerifier [0x7ff6d2a751fb+43ee4b]
-	chromedriver!GetHandleVerifier [0x7ff6d2a696ce+43331e]
-	chromedriver!GetHandleVerifier [0x7ff6d274015e+109dae]
-	chromedriver!(No symbol) [0x7ff6d2570e85]
-	chromedriver!(No symbol) [0x7ff6d256be14]
-	chromedriver!(No symbol) [0x7ff6d256bfa4]
-	chromedriver!(No symbol) [0x7ff6d2556b0c]
+	chromedriver!GetHandleVerifier [0x7ff6b6a3be05+5a55]
+	chromedriver!(No symbol) [0x7ff6b6963230]
+	chromedriver!(No symbol) [0x7ff6b6786e4d]
+	chromedriver!(No symbol) [0x7ff6b6772802]
+	chromedriver!(No symbol) [0x7ff6b67984dc]
+	chromedriver!(No symbol) [0x7ff6b68133c0]
+	chromedriver!(No symbol) [0x7ff6b6831f4d]
+	chromedriver!(No symbol) [0x7ff6b67d4412]
+	chromedriver!(No symbol) [0x7ff6b67d5223]
+	chromedriver!GetHandleVerifier [0x7ff6b6e4b1d1+414e21]
+	chromedriver!GetHandleVerifier [0x7ff6b6e751fb+43ee4b]
+	chromedriver!GetHandleVerifier [0x7ff6b6e696ce+43331e]
+	chromedriver!GetHandleVerifier [0x7ff6b6b4015e+109dae]
+	chromedriver!(No symbol) [0x7ff6b6970e85]
+	chromedriver!(No symbol) [0x7ff6b696be14]
+	chromedriver!(No symbol) [0x7ff6b696bfa4]
+	chromedriver!(No symbol) [0x7ff6b6956b0c]
 	KERNEL32!BaseThreadInitThunk [0x7ff9f5fdcd87+17]
 	ntdll!RtlUserThreadStart [0x7ff9f740caec+2c]
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Error: Message: invalid session id; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#invalidsessionidexception
+Stacktrace:
+	chromedriver!GetHandleVerifier [0x7ff6b6a3be05+5a55]
+	chromedriver!(No symbol) [0x7ff6b6963230]
+	chromedriver!(No symbol) [0x7ff6b6786c46]
+	chromedriver!(No symbol) [0x7ff6b67d3513]
+	chromedriver!(No symbol) [0x7ff6b680b972]
+	chromedriver!(No symbol) [0x7ff6b6805752]
+	chromedriver!(No symbol) [0x7ff6b6804ed3]
+	chromedriver!(No symbol) [0x7ff6b674f16b]
+	chromedriver!(No symbol) [0x7ff6b674f7c2]
+	chromedriver!(No symbol) [0x7ff6b674fdf5]
+	chromedriver!GetHandleVerifier [0x7ff6b6e4b1d1+414e21]
+	chromedriver!GetHandleVerifier [0x7ff6b6e751fb+43ee4b]
+	chromedriver!GetHandleVerifier [0x7ff6b6e696ce+43331e]
+	chromedriver!GetHandleVerifier [0x7ff6b6b4015e+109dae]
+	chromedriver!(No symbol) [0x7ff6b6970e85]
+	chromedriver!(No symbol) [0x7ff6b674e59e]
+	chromedriver!GetHandleVerifier [0x7ff6b6ee5bdf+4af82f]
+	KERNEL32!BaseThreadInitThunk [0x7ff9f5fdcd87+17]
+	ntdll!RtlUserThreadStart [0x7ff9f740caec+2c]
+</t>
+  </si>
+  <si>
+    <t>£34.99</t>
+  </si>
+  <si>
+    <t>£45.83</t>
+  </si>
+  <si>
+    <t>£43.99</t>
+  </si>
+  <si>
+    <t>£62.49</t>
+  </si>
+  <si>
+    <t>£59.99</t>
+  </si>
+  <si>
+    <t>£39.16 presale price: £41.66</t>
+  </si>
+  <si>
+    <t>£47.24</t>
+  </si>
+  <si>
+    <t>£22.49</t>
+  </si>
+  <si>
+    <t>£33.33 presale price: £41.66</t>
+  </si>
+  <si>
+    <t>£1290.75</t>
+  </si>
+  <si>
+    <t>£31.82</t>
+  </si>
+  <si>
+    <t>£30.37</t>
+  </si>
+  <si>
+    <t>£24.1</t>
+  </si>
+  <si>
+    <t>£48.28</t>
+  </si>
+  <si>
+    <t>£46.78</t>
+  </si>
+  <si>
+    <t>£44.26</t>
+  </si>
+  <si>
+    <t>£38.17</t>
+  </si>
+  <si>
+    <t>£869.2</t>
+  </si>
+  <si>
+    <t>£888.6</t>
+  </si>
+  <si>
+    <t>£694.44</t>
+  </si>
+  <si>
+    <t>£449.88</t>
+  </si>
+  <si>
+    <t>£1044.96</t>
+  </si>
+  <si>
+    <t>£179.08</t>
+  </si>
+  <si>
+    <t>£131.78</t>
+  </si>
+  <si>
+    <t>£93.0</t>
+  </si>
+  <si>
+    <t>£9.23</t>
+  </si>
+  <si>
+    <t>£11.25</t>
+  </si>
+  <si>
+    <t>£9.58</t>
+  </si>
+  <si>
     <t>£31.34</t>
   </si>
   <si>
@@ -568,160 +654,118 @@
     <t>£35.8</t>
   </si>
   <si>
+    <t>£32.83</t>
+  </si>
+  <si>
+    <t>£918.0</t>
+  </si>
+  <si>
+    <t>£27.35</t>
+  </si>
+  <si>
+    <t>£27.69</t>
+  </si>
+  <si>
+    <t>£28.3</t>
+  </si>
+  <si>
+    <t>£23.7</t>
+  </si>
+  <si>
+    <t>£47.43</t>
+  </si>
+  <si>
+    <t>£42.65</t>
+  </si>
+  <si>
+    <t>£39.27</t>
+  </si>
+  <si>
+    <t>£704.52</t>
+  </si>
+  <si>
+    <t>£497.88</t>
+  </si>
+  <si>
+    <t>£447.36</t>
+  </si>
+  <si>
+    <t>£715.74</t>
+  </si>
+  <si>
+    <t>£187.8</t>
+  </si>
+  <si>
+    <t>£174.96</t>
+  </si>
+  <si>
+    <t>£157.14</t>
+  </si>
+  <si>
+    <t>£128.5</t>
+  </si>
+  <si>
+    <t>£182.0</t>
+  </si>
+  <si>
+    <t>£128.0</t>
+  </si>
+  <si>
+    <t>£87.5</t>
+  </si>
+  <si>
+    <t>£8.88</t>
+  </si>
+  <si>
+    <t>£6.42</t>
+  </si>
+  <si>
+    <t>£9.68</t>
+  </si>
+  <si>
+    <t>£9.38</t>
+  </si>
+  <si>
+    <t>£44.97</t>
+  </si>
+  <si>
+    <t>£64.27</t>
+  </si>
+  <si>
+    <t>£36.84</t>
+  </si>
+  <si>
+    <t>£35.06</t>
+  </si>
+  <si>
+    <t>£876.5</t>
+  </si>
+  <si>
+    <t>£28.73</t>
+  </si>
+  <si>
+    <t>£49.49</t>
+  </si>
+  <si>
+    <t>£30.91</t>
+  </si>
+  <si>
+    <t>£741.84</t>
+  </si>
+  <si>
+    <t>£460.2</t>
+  </si>
+  <si>
+    <t>£1018.56</t>
+  </si>
+  <si>
     <t>POA</t>
   </si>
   <si>
-    <t>£32.83</t>
-  </si>
-  <si>
-    <t>£918.0</t>
-  </si>
-  <si>
-    <t>£27.35</t>
-  </si>
-  <si>
-    <t>£27.69</t>
-  </si>
-  <si>
-    <t>£28.3</t>
-  </si>
-  <si>
-    <t>£23.7</t>
-  </si>
-  <si>
-    <t>£47.43</t>
-  </si>
-  <si>
-    <t>£42.65</t>
-  </si>
-  <si>
-    <t>£39.27</t>
-  </si>
-  <si>
-    <t>£497.88</t>
-  </si>
-  <si>
-    <t>£447.36</t>
-  </si>
-  <si>
-    <t>£715.74</t>
-  </si>
-  <si>
-    <t>£187.8</t>
-  </si>
-  <si>
-    <t>£174.96</t>
-  </si>
-  <si>
-    <t>£157.14</t>
-  </si>
-  <si>
-    <t>£128.5</t>
-  </si>
-  <si>
-    <t>£182.0</t>
-  </si>
-  <si>
-    <t>£128.0</t>
-  </si>
-  <si>
-    <t>£87.5</t>
-  </si>
-  <si>
-    <t>£8.88</t>
-  </si>
-  <si>
-    <t>£6.42</t>
-  </si>
-  <si>
-    <t>£9.68</t>
-  </si>
-  <si>
-    <t>£9.38</t>
-  </si>
-  <si>
-    <t>£44.97</t>
-  </si>
-  <si>
-    <t>£44.52</t>
-  </si>
-  <si>
-    <t>£44.89</t>
-  </si>
-  <si>
-    <t>£64.27</t>
-  </si>
-  <si>
-    <t>£61.16</t>
-  </si>
-  <si>
-    <t>£95.92</t>
-  </si>
-  <si>
-    <t>£86.21</t>
-  </si>
-  <si>
-    <t>£48.06</t>
-  </si>
-  <si>
-    <t>£27.94</t>
-  </si>
-  <si>
-    <t>£46.61</t>
-  </si>
-  <si>
-    <t>£1243.25</t>
-  </si>
-  <si>
-    <t>£28.73</t>
-  </si>
-  <si>
-    <t>£31.56</t>
-  </si>
-  <si>
-    <t>£36.85</t>
-  </si>
-  <si>
-    <t>£31.24</t>
-  </si>
-  <si>
-    <t>£49.49</t>
-  </si>
-  <si>
-    <t>£44.11</t>
-  </si>
-  <si>
-    <t>£41.22</t>
-  </si>
-  <si>
-    <t>£30.66</t>
-  </si>
-  <si>
-    <t>£741.84</t>
-  </si>
-  <si>
-    <t>£1460.4</t>
-  </si>
-  <si>
-    <t>£631.2</t>
-  </si>
-  <si>
-    <t>£484.2</t>
-  </si>
-  <si>
-    <t>£434.28</t>
-  </si>
-  <si>
-    <t>£996.96</t>
-  </si>
-  <si>
-    <t>Error: list index out of range</t>
-  </si>
-  <si>
     <t>£7.36</t>
   </si>
   <si>
-    <t>£8.58</t>
+    <t>£5.2</t>
   </si>
   <si>
     <t>£13.05</t>
@@ -853,9 +897,6 @@
     <t>£36.0</t>
   </si>
   <si>
-    <t>£22.49</t>
-  </si>
-  <si>
     <t>£33.33</t>
   </si>
   <si>
@@ -880,12 +921,12 @@
     <t>£554.76</t>
   </si>
   <si>
-    <t>£449.88</t>
-  </si>
-  <si>
     <t>£817.92</t>
   </si>
   <si>
+    <t>Price Not Found</t>
+  </si>
+  <si>
     <t>£187.58</t>
   </si>
   <si>
@@ -902,9 +943,6 @@
   </si>
   <si>
     <t>£9.4</t>
-  </si>
-  <si>
-    <t>Error: 'NoneType' object has no attribute 'find'</t>
   </si>
 </sst>
 </file>
@@ -1311,22 +1349,22 @@
         <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F2" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G2" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="H2" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="J2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1343,22 +1381,22 @@
         <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G3" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="H3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I3" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="J3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1375,22 +1413,22 @@
         <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H4" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="J4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1407,22 +1445,22 @@
         <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="F5" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G5" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="H5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="I5" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="J5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1439,22 +1477,22 @@
         <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="G6" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="H6" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="I6" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="J6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1471,22 +1509,22 @@
         <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F7" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="G7" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="H7" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="I7" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="J7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1503,22 +1541,22 @@
         <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="G8" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="H8" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="I8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="J8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1535,22 +1573,22 @@
         <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F9" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="G9" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="H9" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="I9" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="J9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1567,22 +1605,22 @@
         <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F10" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="G10" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="H10" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="I10" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="J10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1602,19 +1640,19 @@
         <v>170</v>
       </c>
       <c r="F11" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="G11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H11" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="I11" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="J11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1631,22 +1669,22 @@
         <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F12" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="G12" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="H12" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="I12" t="s">
-        <v>272</v>
+        <v>171</v>
       </c>
       <c r="J12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1660,25 +1698,25 @@
         <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F13" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="H13" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="I13" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="J13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1692,25 +1730,25 @@
         <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F14" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="G14" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="H14" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="I14" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="J14" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1724,25 +1762,25 @@
         <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F15" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G15" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="H15" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="I15" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="J15" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1756,25 +1794,25 @@
         <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F16" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="G16" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="H16" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="I16" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="J16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1788,25 +1826,25 @@
         <v>113</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F17" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="G17" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="H17" t="s">
         <v>113</v>
       </c>
       <c r="I17" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="J17" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1820,25 +1858,25 @@
         <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F18" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="G18" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="H18" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="I18" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="J18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1852,25 +1890,25 @@
         <v>115</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F19" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="G19" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="I19" t="s">
         <v>115</v>
       </c>
       <c r="J19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1884,25 +1922,25 @@
         <v>116</v>
       </c>
       <c r="D20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="F20" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="G20" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="H20" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="I20" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="J20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1916,25 +1954,25 @@
         <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F21" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="G21" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="H21" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="I21" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="J21" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1951,22 +1989,22 @@
         <v>147</v>
       </c>
       <c r="E22" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G22" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="H22" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="I22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1980,25 +2018,25 @@
         <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="F23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G23" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="H23" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="I23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -2012,25 +2050,25 @@
         <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E24" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G24" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H24" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="I24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J24" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -2044,25 +2082,25 @@
         <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F25" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="G25" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="H25" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="I25" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="J25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -2076,25 +2114,25 @@
         <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="F26" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="G26" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="H26" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="I26" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="J26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -2108,25 +2146,25 @@
         <v>123</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E27" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="F27" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="G27" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="H27" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="I27" t="s">
-        <v>281</v>
+        <v>184</v>
       </c>
       <c r="J27" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -2140,25 +2178,25 @@
         <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E28" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="F28" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="G28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="H28" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="I28" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -2172,25 +2210,25 @@
         <v>125</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F29" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="G29" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H29" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="I29" t="s">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="J29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -2204,25 +2242,25 @@
         <v>126</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F30" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H30" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="I30" t="s">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="J30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -2236,25 +2274,25 @@
         <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F31" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="G31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H31" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="I31" t="s">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="J31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -2268,25 +2306,25 @@
         <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F32" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="G32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H32" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="I32" t="s">
-        <v>168</v>
+        <v>288</v>
       </c>
       <c r="J32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -2300,25 +2338,25 @@
         <v>129</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="F33" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="G33" t="s">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="H33" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="I33" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="J33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -2332,25 +2370,25 @@
         <v>130</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E34" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="F34" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="G34" t="s">
-        <v>177</v>
+        <v>233</v>
       </c>
       <c r="H34" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="I34" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="J34" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -2364,25 +2402,25 @@
         <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="F35" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="G35" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="H35" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="I35" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="J35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -2396,25 +2434,25 @@
         <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E36" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="F36" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="G36" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H36" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="I36" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="J36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -2428,25 +2466,25 @@
         <v>133</v>
       </c>
       <c r="D37" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E37" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="F37" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="G37" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="H37" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I37" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="J37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -2460,25 +2498,25 @@
         <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E38" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="F38" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="G38" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="H38" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="I38" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="J38" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:10">
@@ -2492,25 +2530,25 @@
         <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E39" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F39" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="G39" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="H39" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I39" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="J39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:10">
@@ -2524,25 +2562,25 @@
         <v>136</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="E40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I40" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="41" spans="1:10">
@@ -2556,25 +2594,25 @@
         <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J41" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:10">
@@ -2588,25 +2626,25 @@
         <v>138</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -2620,25 +2658,25 @@
         <v>139</v>
       </c>
       <c r="D43" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I43" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="44" spans="1:10">
@@ -2652,25 +2690,25 @@
         <v>140</v>
       </c>
       <c r="D44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I44" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -2684,25 +2722,25 @@
         <v>141</v>
       </c>
       <c r="D45" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I45" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J45" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -2716,25 +2754,25 @@
         <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I46" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_29-09-2026.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_29-09-2026.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Core-Products_Prices\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF16210-3C5E-4C1B-8290-54903A3D5705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="690" yWindow="1710" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="326">
   <si>
     <t>SKU</t>
   </si>
@@ -502,56 +508,6 @@
     <t>£150.00</t>
   </si>
   <si>
-    <t xml:space="preserve">Error: Message: invalid session id: session deleted as the browser has closed the connection
-from disconnected: not connected to DevTools
-  (Session info: chrome=154.0.8037.58); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#invalidsessionidexception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6b6a3be05+5a55]
-	chromedriver!(No symbol) [0x7ff6b6963230]
-	chromedriver!(No symbol) [0x7ff6b6786e4d]
-	chromedriver!(No symbol) [0x7ff6b6772802]
-	chromedriver!(No symbol) [0x7ff6b67984dc]
-	chromedriver!(No symbol) [0x7ff6b68133c0]
-	chromedriver!(No symbol) [0x7ff6b6831f4d]
-	chromedriver!(No symbol) [0x7ff6b67d4412]
-	chromedriver!(No symbol) [0x7ff6b67d5223]
-	chromedriver!GetHandleVerifier [0x7ff6b6e4b1d1+414e21]
-	chromedriver!GetHandleVerifier [0x7ff6b6e751fb+43ee4b]
-	chromedriver!GetHandleVerifier [0x7ff6b6e696ce+43331e]
-	chromedriver!GetHandleVerifier [0x7ff6b6b4015e+109dae]
-	chromedriver!(No symbol) [0x7ff6b6970e85]
-	chromedriver!(No symbol) [0x7ff6b696be14]
-	chromedriver!(No symbol) [0x7ff6b696bfa4]
-	chromedriver!(No symbol) [0x7ff6b6956b0c]
-	KERNEL32!BaseThreadInitThunk [0x7ff9f5fdcd87+17]
-	ntdll!RtlUserThreadStart [0x7ff9f740caec+2c]
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error: Message: invalid session id; For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#invalidsessionidexception
-Stacktrace:
-	chromedriver!GetHandleVerifier [0x7ff6b6a3be05+5a55]
-	chromedriver!(No symbol) [0x7ff6b6963230]
-	chromedriver!(No symbol) [0x7ff6b6786c46]
-	chromedriver!(No symbol) [0x7ff6b67d3513]
-	chromedriver!(No symbol) [0x7ff6b680b972]
-	chromedriver!(No symbol) [0x7ff6b6805752]
-	chromedriver!(No symbol) [0x7ff6b6804ed3]
-	chromedriver!(No symbol) [0x7ff6b674f16b]
-	chromedriver!(No symbol) [0x7ff6b674f7c2]
-	chromedriver!(No symbol) [0x7ff6b674fdf5]
-	chromedriver!GetHandleVerifier [0x7ff6b6e4b1d1+414e21]
-	chromedriver!GetHandleVerifier [0x7ff6b6e751fb+43ee4b]
-	chromedriver!GetHandleVerifier [0x7ff6b6e696ce+43331e]
-	chromedriver!GetHandleVerifier [0x7ff6b6b4015e+109dae]
-	chromedriver!(No symbol) [0x7ff6b6970e85]
-	chromedriver!(No symbol) [0x7ff6b674e59e]
-	chromedriver!GetHandleVerifier [0x7ff6b6ee5bdf+4af82f]
-	KERNEL32!BaseThreadInitThunk [0x7ff9f5fdcd87+17]
-	ntdll!RtlUserThreadStart [0x7ff9f740caec+2c]
-</t>
-  </si>
-  <si>
     <t>£34.99</t>
   </si>
   <si>
@@ -943,13 +899,112 @@
   </si>
   <si>
     <t>£9.4</t>
+  </si>
+  <si>
+    <t>£30.96</t>
+  </si>
+  <si>
+    <t>£30.52</t>
+  </si>
+  <si>
+    <t>£44.01</t>
+  </si>
+  <si>
+    <t>£43.18</t>
+  </si>
+  <si>
+    <t>£57.04</t>
+  </si>
+  <si>
+    <t>£54.82</t>
+  </si>
+  <si>
+    <t>£35.22</t>
+  </si>
+  <si>
+    <t>£37.37</t>
+  </si>
+  <si>
+    <t>£37.66</t>
+  </si>
+  <si>
+    <t>£29.96</t>
+  </si>
+  <si>
+    <t>£28.76</t>
+  </si>
+  <si>
+    <t>£23.5</t>
+  </si>
+  <si>
+    <t>£43.36</t>
+  </si>
+  <si>
+    <t>£42.01</t>
+  </si>
+  <si>
+    <t>£37.01</t>
+  </si>
+  <si>
+    <t>£198.59</t>
+  </si>
+  <si>
+    <t>£186.0</t>
+  </si>
+  <si>
+    <t>£173.05</t>
+  </si>
+  <si>
+    <t>£138.57</t>
+  </si>
+  <si>
+    <t>£132.69</t>
+  </si>
+  <si>
+    <t>£88.75</t>
+  </si>
+  <si>
+    <t>£10.03</t>
+  </si>
+  <si>
+    <t>£4.64</t>
+  </si>
+  <si>
+    <t>£11.0</t>
+  </si>
+  <si>
+    <t>£11.08</t>
+  </si>
+  <si>
+    <t>£14.0</t>
+  </si>
+  <si>
+    <t>£11.52</t>
+  </si>
+  <si>
+    <t>£11.68</t>
+  </si>
+  <si>
+    <t>£8.69</t>
+  </si>
+  <si>
+    <t>£11.38</t>
+  </si>
+  <si>
+    <t>£94.92</t>
+  </si>
+  <si>
+    <t>£10.75</t>
+  </si>
+  <si>
+    <t>£11.50</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1012,13 +1067,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1056,7 +1119,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1090,6 +1153,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1124,9 +1188,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1299,11 +1364,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1335,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1349,25 +1414,25 @@
         <v>143</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1381,25 +1446,25 @@
         <v>143</v>
       </c>
       <c r="E3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="J3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1413,25 +1478,25 @@
         <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G4" t="s">
         <v>149</v>
       </c>
       <c r="H4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1445,25 +1510,25 @@
         <v>143</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1477,25 +1542,25 @@
         <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="J6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1509,25 +1574,25 @@
         <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="J7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1541,25 +1606,25 @@
         <v>145</v>
       </c>
       <c r="E8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="J8" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1573,25 +1638,25 @@
         <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G9" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="I9" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="J9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1605,25 +1670,25 @@
         <v>147</v>
       </c>
       <c r="E10" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="I10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J10" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1637,25 +1702,25 @@
         <v>147</v>
       </c>
       <c r="E11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G11" t="s">
         <v>149</v>
       </c>
       <c r="H11" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="I11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J11" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1669,25 +1734,25 @@
         <v>148</v>
       </c>
       <c r="E12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I12" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J12" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1701,25 +1766,25 @@
         <v>148</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G13" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H13" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I13" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J13" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1733,25 +1798,25 @@
         <v>149</v>
       </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F14" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I14" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J14" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1765,25 +1830,25 @@
         <v>150</v>
       </c>
       <c r="E15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F15" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J15" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1797,25 +1862,25 @@
         <v>151</v>
       </c>
       <c r="E16" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G16" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J16" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1829,25 +1894,25 @@
         <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F17" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G17" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H17" t="s">
         <v>113</v>
       </c>
       <c r="I17" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J17" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1861,25 +1926,25 @@
         <v>152</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G18" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H18" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I18" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="J18" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1893,25 +1958,25 @@
         <v>153</v>
       </c>
       <c r="E19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="I19" t="s">
         <v>115</v>
       </c>
       <c r="J19" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -1925,25 +1990,25 @@
         <v>153</v>
       </c>
       <c r="E20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J20" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1957,25 +2022,25 @@
         <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I21" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J21" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1989,16 +2054,16 @@
         <v>147</v>
       </c>
       <c r="E22" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F22" t="s">
         <v>149</v>
       </c>
       <c r="G22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H22" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I22" t="s">
         <v>149</v>
@@ -2007,7 +2072,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2021,16 +2086,16 @@
         <v>149</v>
       </c>
       <c r="E23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F23" t="s">
         <v>149</v>
       </c>
       <c r="G23" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="I23" t="s">
         <v>149</v>
@@ -2039,7 +2104,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2053,16 +2118,16 @@
         <v>155</v>
       </c>
       <c r="E24" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F24" t="s">
         <v>149</v>
       </c>
       <c r="G24" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H24" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I24" t="s">
         <v>149</v>
@@ -2071,7 +2136,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2085,25 +2150,25 @@
         <v>149</v>
       </c>
       <c r="E25" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F25" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G25" t="s">
+        <v>229</v>
+      </c>
+      <c r="H25" t="s">
+        <v>255</v>
+      </c>
+      <c r="I25" t="s">
+        <v>283</v>
+      </c>
+      <c r="J25" t="s">
         <v>231</v>
       </c>
-      <c r="H25" t="s">
-        <v>257</v>
-      </c>
-      <c r="I25" t="s">
-        <v>285</v>
-      </c>
-      <c r="J25" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2117,25 +2182,25 @@
         <v>149</v>
       </c>
       <c r="E26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F26" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G26" t="s">
+        <v>229</v>
+      </c>
+      <c r="H26" t="s">
+        <v>256</v>
+      </c>
+      <c r="I26" t="s">
+        <v>284</v>
+      </c>
+      <c r="J26" t="s">
         <v>231</v>
       </c>
-      <c r="H26" t="s">
-        <v>258</v>
-      </c>
-      <c r="I26" t="s">
-        <v>286</v>
-      </c>
-      <c r="J26" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2149,25 +2214,25 @@
         <v>156</v>
       </c>
       <c r="E27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F27" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G27" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H27" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J27" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2181,25 +2246,25 @@
         <v>149</v>
       </c>
       <c r="E28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F28" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G28" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H28" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="J28" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2216,22 +2281,22 @@
         <v>149</v>
       </c>
       <c r="F29" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G29" t="s">
         <v>149</v>
       </c>
       <c r="H29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J29" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2248,22 +2313,22 @@
         <v>149</v>
       </c>
       <c r="F30" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G30" t="s">
         <v>149</v>
       </c>
       <c r="H30" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J30" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2280,22 +2345,22 @@
         <v>149</v>
       </c>
       <c r="F31" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G31" t="s">
         <v>149</v>
       </c>
       <c r="H31" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J31" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2312,22 +2377,22 @@
         <v>149</v>
       </c>
       <c r="F32" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G32" t="s">
         <v>149</v>
       </c>
       <c r="H32" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I32" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="J32" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2341,25 +2406,25 @@
         <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F33" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G33" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H33" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I33" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="J33" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2373,25 +2438,25 @@
         <v>161</v>
       </c>
       <c r="E34" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G34" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H34" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I34" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J34" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2402,28 +2467,28 @@
         <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>323</v>
       </c>
       <c r="E35" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F35" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H35" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I35" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J35" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2434,28 +2499,28 @@
         <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="E36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F36" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H36" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I36" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J36" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2469,25 +2534,25 @@
         <v>149</v>
       </c>
       <c r="E37" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G37" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H37" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I37" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J37" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2498,28 +2563,28 @@
         <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>324</v>
       </c>
       <c r="E38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H38" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I38" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J38" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2530,28 +2595,28 @@
         <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>325</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F39" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G39" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H39" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I39" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J39" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2580,10 +2645,10 @@
         <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -2612,10 +2677,10 @@
         <v>149</v>
       </c>
       <c r="J41" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2644,10 +2709,10 @@
         <v>149</v>
       </c>
       <c r="J42" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2676,10 +2741,10 @@
         <v>149</v>
       </c>
       <c r="J43" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2708,10 +2773,10 @@
         <v>149</v>
       </c>
       <c r="J44" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2740,10 +2805,10 @@
         <v>149</v>
       </c>
       <c r="J45" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -2772,7 +2837,7 @@
         <v>149</v>
       </c>
       <c r="J46" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
